--- a/data/trans_orig/IP07C08-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07C08-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haberse ayudado entre los amigos en 2007 (tasa de respuesta: 89,69%)</t>
+          <t>Menores según la frecuencia de haberse ayudado entre los/as amigos/as en 2007 (tasa de respuesta: 89,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39239</t>
+          <t>38825</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>56030</t>
+          <t>55404</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34826</t>
+          <t>34668</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52247</t>
+          <t>51423</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>78405</t>
+          <t>77640</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>102463</t>
+          <t>102930</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>43,89%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40134</t>
+          <t>40852</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56941</t>
+          <t>57367</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48122</t>
+          <t>49422</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>66466</t>
+          <t>66841</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>93475</t>
+          <t>93872</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>118319</t>
+          <t>118769</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>50,64%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9777</t>
+          <t>9415</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20577</t>
+          <t>20753</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13192</t>
+          <t>13245</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26323</t>
+          <t>26168</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>25832</t>
+          <t>26203</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>43067</t>
+          <t>43155</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>4062</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>587</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6612</t>
+          <t>6448</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1374</t>
+          <t>1758</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>8435</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3396</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3885</t>
+          <t>3441</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57272</t>
+          <t>56442</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>78394</t>
+          <t>77003</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63021</t>
+          <t>63456</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>85019</t>
+          <t>85724</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>125405</t>
+          <t>126961</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>156399</t>
+          <t>156584</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>42,98%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79115</t>
+          <t>80174</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>100879</t>
+          <t>100330</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>80226</t>
+          <t>79517</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>101895</t>
+          <t>102367</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>55,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>163813</t>
+          <t>165206</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>196621</t>
+          <t>195735</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>53,73%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12775</t>
+          <t>13111</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26574</t>
+          <t>26672</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12789</t>
+          <t>12640</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25878</t>
+          <t>26252</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>29358</t>
+          <t>29105</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>48590</t>
+          <t>48262</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5810</t>
+          <t>5319</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3239</t>
+          <t>2977</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>706</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6275</t>
+          <t>6884</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2921</t>
+          <t>3691</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3881</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5348</t>
+          <t>4744</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>100604</t>
+          <t>99120</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>126536</t>
+          <t>127464</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>105042</t>
+          <t>105372</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>132332</t>
+          <t>132408</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>211862</t>
+          <t>211575</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>249789</t>
+          <t>249427</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,65%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>124980</t>
+          <t>125719</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>151718</t>
+          <t>154353</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>134902</t>
+          <t>134809</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>161484</t>
+          <t>162628</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>268570</t>
+          <t>269841</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>306873</t>
+          <t>309473</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>51,68%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26146</t>
+          <t>25664</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>42995</t>
+          <t>43464</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>29544</t>
+          <t>29316</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>48170</t>
+          <t>47211</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>59487</t>
+          <t>59463</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>85149</t>
+          <t>84762</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,15%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7376</t>
+          <t>7321</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1157</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7129</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3168</t>
+          <t>3190</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11912</t>
+          <t>11828</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3727</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4920</t>
+          <t>4776</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>659</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6116</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haberse ayudado entre los amigos en 2012 (tasa de respuesta: 95,52%)</t>
+          <t>Menores según la frecuencia de haberse ayudado entre los/as amigos/as en 2012 (tasa de respuesta: 95,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>65771</t>
+          <t>66996</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>85730</t>
+          <t>86288</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>60089</t>
+          <t>59127</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>80593</t>
+          <t>79742</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>131002</t>
+          <t>131869</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>159368</t>
+          <t>159602</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>52,26%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53292</t>
+          <t>53503</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>73822</t>
+          <t>72372</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46567</t>
+          <t>46791</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>66546</t>
+          <t>67130</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>104319</t>
+          <t>106035</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>133755</t>
+          <t>133419</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>43,69%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5054</t>
+          <t>5287</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15003</t>
+          <t>14908</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19568</t>
+          <t>20073</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35002</t>
+          <t>35967</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>28212</t>
+          <t>27344</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>47094</t>
+          <t>46536</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>586</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4880</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3459</t>
+          <t>3690</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>608</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6340</t>
+          <t>6045</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>621</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6286</t>
+          <t>5788</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5606</t>
+          <t>5631</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55200</t>
+          <t>54791</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>75768</t>
+          <t>74796</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>68707</t>
+          <t>68753</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>90788</t>
+          <t>90213</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>128530</t>
+          <t>129974</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>158878</t>
+          <t>159940</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>48,25%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66337</t>
+          <t>68071</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>87494</t>
+          <t>88216</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60036</t>
+          <t>59784</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>80374</t>
+          <t>80334</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>133287</t>
+          <t>131926</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>163972</t>
+          <t>161916</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>48,85%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8425</t>
+          <t>8369</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19757</t>
+          <t>19974</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10918</t>
+          <t>10704</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24046</t>
+          <t>23271</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>22306</t>
+          <t>21696</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>39701</t>
+          <t>39295</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,85%</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>602</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>5137</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>1863</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8064</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>3144</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10609</t>
+          <t>11188</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>762</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6753</t>
+          <t>6737</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>3649</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>1426</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8228</t>
+          <t>7519</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>126732</t>
+          <t>125399</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>154780</t>
+          <t>155208</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>134506</t>
+          <t>134379</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>164330</t>
+          <t>163929</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>269592</t>
+          <t>267706</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>310401</t>
+          <t>310286</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>48,72%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>125334</t>
+          <t>126044</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>154976</t>
+          <t>156359</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>110168</t>
+          <t>112337</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>140885</t>
+          <t>140199</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>245461</t>
+          <t>246755</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>285863</t>
+          <t>288349</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>45,28%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16219</t>
+          <t>17035</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30756</t>
+          <t>31349</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>33383</t>
+          <t>33139</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>53101</t>
+          <t>54614</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>53985</t>
+          <t>55041</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>79786</t>
+          <t>79282</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7712</t>
+          <t>7363</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2488</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9965</t>
+          <t>9132</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14267</t>
+          <t>14626</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>724</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6662</t>
+          <t>6637</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>775</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6974</t>
+          <t>7036</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2185</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10919</t>
+          <t>11035</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haberse ayudado entre los amigos en 2016 (tasa de respuesta: 95,47%)</t>
+          <t>Menores según la frecuencia de haberse ayudado entre los/as amigos/as en 2016 (tasa de respuesta: 95,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>85238</t>
+          <t>85405</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>106988</t>
+          <t>107956</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>86165</t>
+          <t>85768</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>107584</t>
+          <t>107682</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>177604</t>
+          <t>176487</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>209772</t>
+          <t>206466</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>57,43%</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56065</t>
+          <t>57202</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77720</t>
+          <t>77129</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48829</t>
+          <t>48504</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>69589</t>
+          <t>69532</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>110596</t>
+          <t>111633</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>141224</t>
+          <t>141024</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,23%</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9319</t>
+          <t>9419</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21758</t>
+          <t>21737</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11536</t>
+          <t>12274</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24781</t>
+          <t>26050</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>24092</t>
+          <t>23754</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>43082</t>
+          <t>41627</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4553</t>
+          <t>4612</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1446</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8743</t>
+          <t>8430</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2803</t>
+          <t>2822</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10887</t>
+          <t>10868</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4508</t>
+          <t>3933</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3822</t>
+          <t>4280</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5942</t>
+          <t>6186</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>62286</t>
+          <t>62221</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>84344</t>
+          <t>84163</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>68546</t>
+          <t>69600</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>91593</t>
+          <t>91518</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>138582</t>
+          <t>139070</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>168713</t>
+          <t>168795</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>50,62%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58141</t>
+          <t>59615</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>79901</t>
+          <t>80938</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57367</t>
+          <t>57233</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>80032</t>
+          <t>79322</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>123313</t>
+          <t>123095</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>151638</t>
+          <t>152502</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>45,73%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13226</t>
+          <t>13413</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27106</t>
+          <t>27506</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11801</t>
+          <t>11456</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25193</t>
+          <t>24995</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>28450</t>
+          <t>28818</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>47805</t>
+          <t>48082</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,42%</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>3291</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>707</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7783</t>
+          <t>7631</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6355,12 +6355,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8494</t>
+          <t>8702</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3110</t>
+          <t>3432</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6438,77 +6438,77 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
           <t>1,89%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>636</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1253</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3199</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>4409</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1253</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>4421</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>153574</t>
+          <t>154255</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>185605</t>
+          <t>185656</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>159736</t>
+          <t>160037</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>190683</t>
+          <t>191912</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>324735</t>
+          <t>323165</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>367413</t>
+          <t>367519</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>53,04%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>121985</t>
+          <t>121276</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>153216</t>
+          <t>151444</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>114035</t>
+          <t>111644</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>145438</t>
+          <t>142613</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>243733</t>
+          <t>244634</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>284899</t>
+          <t>285625</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,22%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25210</t>
+          <t>26417</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>45199</t>
+          <t>44878</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>27295</t>
+          <t>27140</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>45198</t>
+          <t>46065</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>58251</t>
+          <t>58354</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>84399</t>
+          <t>85186</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -6987,12 +6987,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>683</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6654</t>
+          <t>5670</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3492</t>
+          <t>3868</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12763</t>
+          <t>13442</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7037,12 +7037,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>5111</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16296</t>
+          <t>16058</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -7100,12 +7100,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>614</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5666</t>
+          <t>4962</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>545</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4839</t>
+          <t>5087</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7596</t>
+          <t>7562</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07C08-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07C08-Edad-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de haberse ayudado entre los/as amigos/as en 2007 (tasa de respuesta: 89,69%)</t>
+          <t>Menores según la frecuencia de haberse ayudado entre los/as amigos/as, percibida por el/la menor en 2007 (tasa de respuesta: 89,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>43314</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>35348</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>52117</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>35,08%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>28,63%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>42,21%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>46575</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>38825</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>55404</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>38609</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>54355</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>41,94%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>34,96%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>49,89%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>43314</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>34668</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>51423</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>35,08%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>77640</t>
+          <t>78786</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>102930</t>
+          <t>101683</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>43,35%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>57535</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>48518</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>66166</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>46,59%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>39,29%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>53,58%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>48944</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>40852</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>57367</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>40751</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>57786</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>44,07%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>36,78%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>51,66%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>57535</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>49422</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>66841</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>46,59%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>93872</t>
+          <t>94221</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>118769</t>
+          <t>118260</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>50,42%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>19336</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>13319</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>26664</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>15,66%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>10,79%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>21,59%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>14213</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>9415</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>20753</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>9344</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>20960</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>12,8%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>8,48%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>18,69%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>19336</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>13245</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>26168</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>15,66%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>26203</t>
+          <t>25384</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>43155</t>
+          <t>42001</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>17,91%</t>
         </is>
       </c>
     </row>
@@ -1061,72 +1061,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2618</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6780</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5,49%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1325</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4062</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4604</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,19%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,66%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2618</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>587</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6448</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1758</t>
+          <t>1738</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8435</t>
+          <t>7592</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -1174,107 +1174,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2734</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>679</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>3406</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>3393</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>2,76%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>3441</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>123481</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>123481</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>123481</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>167</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>111057</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>111057</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>111057</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>123481</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>123481</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>123481</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>74410</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>64732</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>87371</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>40,14%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>34,92%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>47,13%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>66662</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>56442</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>77003</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>56948</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>77461</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>37,25%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>31,54%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>43,03%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>74410</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>63456</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>85724</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>40,14%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>126961</t>
+          <t>126767</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>156584</t>
+          <t>156147</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>42,86%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>90981</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>79997</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>101027</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>49,08%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>43,15%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>54,5%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>90369</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>80174</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>100330</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>79947</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>100199</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>50,5%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>44,81%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>56,07%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>90981</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>79517</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>102367</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>49,08%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>56,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>165206</t>
+          <t>165022</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>195735</t>
+          <t>196370</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>53,9%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>18700</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>12700</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>26121</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>10,09%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>6,85%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>14,09%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>19270</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>13111</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>26672</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>13303</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>26399</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>10,77%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>7,33%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>14,91%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>18700</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>12640</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>26252</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>10,09%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>29105</t>
+          <t>29447</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>48262</t>
+          <t>48355</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,27%</t>
         </is>
       </c>
     </row>
@@ -1743,72 +1743,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2981</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1974</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>627</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5319</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>629</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5895</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,1%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,35%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>593</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2977</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>630</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6884</t>
+          <t>5657</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -1861,87 +1861,87 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3474</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>661</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3691</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3315</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,37%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1356</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3850</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>2,08%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1356</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4744</t>
+          <t>4742</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>185378</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>185378</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>185378</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>264</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>178935</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>178935</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>178935</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>185378</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>185378</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>185378</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>117723</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>104623</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>131520</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>38,12%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>33,87%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>42,58%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>170</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>113237</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>99120</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>127464</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>100476</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>127149</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>39,05%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>34,18%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>43,95%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>117723</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>105372</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>132408</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>38,12%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>211575</t>
+          <t>210460</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>249427</t>
+          <t>250800</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,88%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>148516</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>134540</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>161155</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>48,09%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>43,56%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>52,18%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>204</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>139312</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>125719</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>154353</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>124913</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>153007</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>48,04%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>43,35%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>53,23%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>148516</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>134809</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>162628</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>48,09%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>269841</t>
+          <t>268018</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>309473</t>
+          <t>309440</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>51,67%</t>
         </is>
       </c>
     </row>
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>38036</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>28963</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>46817</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>12,31%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>9,38%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>15,16%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>33483</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>25664</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>43464</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>25569</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>43552</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>11,55%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>8,85%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>14,99%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>38036</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>29316</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>47211</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>12,31%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>59463</t>
+          <t>58994</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>84762</t>
+          <t>83019</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,86%</t>
         </is>
       </c>
     </row>
@@ -2430,67 +2430,67 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>3211</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1136</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>7213</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
           <t>3298</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1291</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>7321</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1289</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>7101</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,14%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>3211</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>1157</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>7069</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>3394</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11828</t>
+          <t>11201</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -2538,72 +2538,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1374</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>4824</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>661</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3995</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3300</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,23%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>1374</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>4776</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>660</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>5946</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>465</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>308859</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>308859</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>308859</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>431</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>289992</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>289992</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>289992</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>465</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>308859</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>308859</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>308859</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2813,13 +2813,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de haberse ayudado entre los/as amigos/as en 2012 (tasa de respuesta: 95,52%)</t>
+          <t>Menores según la frecuencia de haberse ayudado entre los/as amigos/as, percibida por el/la menor en 2012 (tasa de respuesta: 95,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2830,7 +2830,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2998,72 +2998,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>69603</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>60406</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>79621</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>44,78%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>38,86%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>51,23%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>75963</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>66996</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>86288</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>66891</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>87386</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>50,65%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>44,67%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>57,54%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>69603</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>59127</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>79742</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>44,78%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>131869</t>
+          <t>131150</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>159602</t>
+          <t>159364</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>52,18%</t>
         </is>
       </c>
     </row>
@@ -3111,72 +3111,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>56004</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>46760</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>67076</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>36,03%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>30,09%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>43,16%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>62759</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>53503</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>72372</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>52283</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>72468</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>41,85%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>35,68%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>48,26%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>56004</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>46791</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>67130</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>36,03%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>106035</t>
+          <t>105208</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>133419</t>
+          <t>133509</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>43,72%</t>
         </is>
       </c>
     </row>
@@ -3224,72 +3224,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>27048</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>19813</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>35846</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>17,4%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>12,75%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>23,06%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>9441</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5287</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>14908</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>5323</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>14543</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>6,3%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>9,94%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>27048</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>20073</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>35967</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>17,4%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27344</t>
+          <t>27030</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>46536</t>
+          <t>46516</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,23%</t>
         </is>
       </c>
     </row>
@@ -3337,72 +3337,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>689</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3457</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1802</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>586</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4870</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4831</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,2%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,39%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,25%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>689</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3690</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>613</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6045</t>
+          <t>6071</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -3450,92 +3450,92 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2082</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5597</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>2082</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>621</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>5788</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>3,72%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>2082</t>
-        </is>
-      </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>623</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5631</t>
+          <t>5645</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -3563,57 +3563,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>155427</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>155427</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>155427</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>214</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>149965</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>149965</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>149965</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>155427</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>155427</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>155427</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3680,72 +3680,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>79786</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>69507</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>90628</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>46,75%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>40,73%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>53,11%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>64924</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>54791</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>74796</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>54086</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>74596</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>40,37%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>34,07%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>46,51%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>79786</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>68753</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>90213</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>46,75%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>129974</t>
+          <t>130488</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>159940</t>
+          <t>160198</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,33%</t>
         </is>
       </c>
     </row>
@@ -3793,72 +3793,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>69636</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>60218</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>80816</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>40,81%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>35,29%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>47,36%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>77546</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>68071</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>88216</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>68267</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>88405</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>48,21%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>42,32%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>54,85%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>69636</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>59784</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>80334</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>40,81%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>131926</t>
+          <t>132585</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>161916</t>
+          <t>162453</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>49,01%</t>
         </is>
       </c>
     </row>
@@ -3906,72 +3906,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>16175</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>10947</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>23168</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>9,48%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>6,42%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>13,58%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>13509</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>8369</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>19974</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>8724</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>20609</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>8,4%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,2%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>12,42%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>16175</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>10704</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>23271</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>9,48%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>21696</t>
+          <t>21806</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>39295</t>
+          <t>38785</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -4019,72 +4019,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4323</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1839</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8548</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5,01%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1896</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>602</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5137</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>606</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5689</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,18%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4323</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1863</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>8210</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3144</t>
+          <t>3141</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11188</t>
+          <t>11132</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -4132,107 +4132,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>731</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3685</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2,16%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>2959</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>762</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6737</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>765</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>7446</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>1,84%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>4,19%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>731</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3649</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>4,63%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>3689</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1438</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>8108</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,43%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>3689</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1426</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>7519</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -4245,57 +4245,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>170651</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>170651</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>170651</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>228</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>160834</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>160834</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>160834</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>170651</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>170651</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>170651</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4362,72 +4362,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>149390</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>133464</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>162119</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>45,81%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>40,93%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>49,72%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>199</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>140887</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>125399</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>155208</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>126600</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>154887</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>45,33%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>40,35%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>49,94%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>149390</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>134379</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>163929</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>45,81%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>267706</t>
+          <t>272032</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>310286</t>
+          <t>312876</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>49,13%</t>
         </is>
       </c>
     </row>
@@ -4475,72 +4475,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>125640</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>111819</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>141112</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>38,53%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>34,29%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>43,28%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>199</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>140305</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>126044</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>156359</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>126617</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>155094</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>45,14%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>40,55%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>50,31%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>125640</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>112337</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>140199</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>38,53%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>246755</t>
+          <t>245713</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>288349</t>
+          <t>285354</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>44,81%</t>
         </is>
       </c>
     </row>
@@ -4588,72 +4588,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>43224</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>33787</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>53972</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>13,26%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>10,36%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>16,55%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>22949</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>17035</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>31349</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>16329</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>30532</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>7,38%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>5,48%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>10,09%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>43224</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>33139</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>54614</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>13,26%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>55041</t>
+          <t>54032</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>79282</t>
+          <t>80142</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -4701,72 +4701,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>5012</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2491</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>10024</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>3698</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1304</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>7363</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1281</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>7895</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,19%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>5012</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>2439</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>9132</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5047</t>
+          <t>4955</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14626</t>
+          <t>14318</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -4819,67 +4819,67 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>2813</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>775</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>7297</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
           <t>2959</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>724</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>6637</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>7206</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,95%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,23%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>2813</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>775</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>7036</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2185</t>
+          <t>2244</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11035</t>
+          <t>10795</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -4927,57 +4927,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>474</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>326078</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>326078</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>326078</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>442</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>310798</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>310798</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>310798</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>474</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>326078</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>326078</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>326078</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5089,13 +5089,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de haberse ayudado entre los/as amigos/as en 2016 (tasa de respuesta: 95,47%)</t>
+          <t>Menores según la frecuencia de haberse ayudado entre los/as amigos/as, percibida por el/la menor en 2016 (tasa de respuesta: 95,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5106,7 +5106,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5274,72 +5274,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>96894</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>84745</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>107294</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>54,25%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>47,45%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>60,07%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>95890</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>85405</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>107956</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>84089</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>106602</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>53,01%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>47,21%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>59,68%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>96894</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>85768</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>107682</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>54,25%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>176487</t>
+          <t>177366</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>206466</t>
+          <t>208602</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>58,03%</t>
         </is>
       </c>
     </row>
@@ -5387,72 +5387,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>58471</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>47901</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>69521</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>32,74%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>26,82%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>38,92%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>67384</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>57202</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>77129</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>57955</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>78325</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>37,25%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>31,62%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>42,64%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>58471</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>48504</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>69532</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>32,74%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>111633</t>
+          <t>111839</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>141024</t>
+          <t>141733</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,43%</t>
         </is>
       </c>
     </row>
@@ -5500,72 +5500,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>17820</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>11343</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>25119</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>9,98%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>6,35%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>14,06%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>14831</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>9419</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>21737</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>9524</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>21692</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>8,2%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,21%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>12,02%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>17820</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>12274</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>26050</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>9,98%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23754</t>
+          <t>24320</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>41627</t>
+          <t>42879</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,93%</t>
         </is>
       </c>
     </row>
@@ -5613,72 +5613,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4233</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1545</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>9053</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5,07%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1516</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4612</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5170</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,84%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4233</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1517</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>8430</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2822</t>
+          <t>2806</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10868</t>
+          <t>11003</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -5731,67 +5731,67 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>1193</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4090</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>1267</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3933</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3860</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,7%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1193</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>4280</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>635</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6186</t>
+          <t>5694</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -5839,57 +5839,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>178611</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>178611</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>178611</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>180887</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>180887</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>180887</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>178611</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>178611</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>178611</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5956,72 +5956,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>79469</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>67733</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>89807</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>46,95%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>40,01%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>53,05%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>73292</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>62221</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>84163</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>62561</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>83890</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>44,64%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>37,9%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>51,26%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>79469</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>69600</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>91518</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>46,95%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>139070</t>
+          <t>138167</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>168795</t>
+          <t>168172</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>50,43%</t>
         </is>
       </c>
     </row>
@@ -6069,72 +6069,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>68246</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>57524</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>78906</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>40,32%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>33,98%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>46,61%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>69600</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>59615</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>80938</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>59368</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>80047</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>42,39%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>36,31%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>49,3%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>68246</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>57233</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>79322</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>40,32%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>123095</t>
+          <t>122722</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>152502</t>
+          <t>152590</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,76%</t>
         </is>
       </c>
     </row>
@@ -6182,72 +6182,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>17782</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>11733</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>24862</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>10,5%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>6,93%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>14,69%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>19985</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>13413</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>27506</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>14034</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>28038</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>12,17%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>8,17%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>16,75%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>17782</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>11456</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>24995</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>10,5%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>28818</t>
+          <t>29217</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>48082</t>
+          <t>49545</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,86%</t>
         </is>
       </c>
     </row>
@@ -6295,72 +6295,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3145</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>876</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7700</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,55%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>687</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3291</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3494</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,42%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3145</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>707</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7631</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8702</t>
+          <t>8522</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -6413,102 +6413,102 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3483</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>617</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3432</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3164</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>636</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1253</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3205</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>4183</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1253</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>4409</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -6521,57 +6521,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>169278</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>169278</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>169278</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>164181</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>164181</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>164181</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>169278</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>169278</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>169278</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6638,72 +6638,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>176363</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>160779</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>192521</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>50,7%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>46,22%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>55,34%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>169182</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>154255</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>185656</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>153984</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>183308</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>49,03%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>44,7%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>53,8%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>176363</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>160037</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>191912</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>50,7%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>323165</t>
+          <t>326223</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>367519</t>
+          <t>368835</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>53,23%</t>
         </is>
       </c>
     </row>
@@ -6751,72 +6751,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>126718</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>112215</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>142770</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>36,42%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>32,26%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>41,04%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>197</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>136984</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>121276</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>151444</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>122664</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>152548</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>39,7%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>35,15%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>43,89%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>126718</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>111644</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>142613</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>36,42%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>244634</t>
+          <t>242256</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>285625</t>
+          <t>284457</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>41,05%</t>
         </is>
       </c>
     </row>
@@ -6869,67 +6869,67 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>35603</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>27216</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>45636</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>10,23%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>7,82%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>13,12%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
           <t>34816</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>26417</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>44878</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>26593</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>45586</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>10,09%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>7,66%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>13,01%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>35603</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>27140</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>46065</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>10,23%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>58354</t>
+          <t>57267</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>85186</t>
+          <t>84140</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -6977,72 +6977,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>7378</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>3742</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>13704</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>3,94%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>2202</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>683</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>5670</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>6710</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,64%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>7378</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>3868</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>13442</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5111</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16058</t>
+          <t>15611</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -7095,67 +7095,67 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>1828</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>5509</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
           <t>1884</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>614</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4962</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5057</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,55%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,18%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>5087</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7562</t>
+          <t>7926</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -7203,57 +7203,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>347889</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>347889</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>347889</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>492</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>345068</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>345068</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>345068</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>478</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>347889</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>347889</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>347889</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
